--- a/data/trans_camb/LAWTONB_2R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/LAWTONB_2R2-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,08</t>
+          <t>-2,29</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,89</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,74</t>
+          <t>-1,07</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 4,76</t>
+          <t>-7,03; 5,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,28; -0,9</t>
+          <t>-12,38; -1,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 3,06</t>
+          <t>-7,55; 3,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 6,68</t>
+          <t>-5,24; 6,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 8,21</t>
+          <t>-3,85; 8,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 1,64</t>
+          <t>-5,02; 4,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 4,02</t>
+          <t>-4,54; 4,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 1,97</t>
+          <t>-6,46; 2,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 0,13</t>
+          <t>-4,85; 2,39</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-12,83%</t>
+          <t>-14,14%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-34,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-25,78%</t>
+          <t>-5,83%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 37,91</t>
+          <t>-38,19; 38,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-59,65; -6,57</t>
+          <t>-61,27; -6,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-35,95; 24,56</t>
+          <t>-39,03; 24,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,56; 36,9</t>
+          <t>-23,52; 38,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 46,41</t>
+          <t>-16,72; 47,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,08; 9,5</t>
+          <t>-21,27; 29,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 23,71</t>
+          <t>-22,13; 26,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,11; 12,93</t>
+          <t>-30,49; 14,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-62,42; 0,56</t>
+          <t>-23,23; 14,99</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>-1,53</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,58</t>
+          <t>12,13</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,23</t>
+          <t>6,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 10,92</t>
+          <t>-8,69; 10,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 3,59</t>
+          <t>-13,47; 4,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 7,85</t>
+          <t>-9,06; 6,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 13,79</t>
+          <t>-1,75; 13,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 7,22</t>
+          <t>-8,6; 7,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,61; 18,84</t>
+          <t>5,53; 19,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 9,85</t>
+          <t>-2,27; 9,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 4,06</t>
+          <t>-8,58; 3,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 12,53</t>
+          <t>1,09; 11,89</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-1,4%</t>
+          <t>-3,78%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 31,14</t>
+          <t>-19,23; 28,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 10,78</t>
+          <t>-29,65; 12,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 21,64</t>
+          <t>-19,61; 19,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 30,94</t>
+          <t>-3,41; 29,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,26; 15,6</t>
+          <t>-16,06; 16,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 42,77</t>
+          <t>10,38; 43,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 23,04</t>
+          <t>-5,08; 22,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 9,4</t>
+          <t>-17,47; 8,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 30,06</t>
+          <t>2,48; 28,69</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>-1,61</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,27</t>
+          <t>6,89</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,84</t>
+          <t>3,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 5,44</t>
+          <t>-5,03; 5,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,56; -0,32</t>
+          <t>-10,62; -0,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 3,79</t>
+          <t>-6,64; 3,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 9,36</t>
+          <t>-1,06; 9,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 6,94</t>
+          <t>-4,02; 6,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,04; 8,69</t>
+          <t>2,34; 11,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 6,28</t>
+          <t>-1,7; 6,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 1,86</t>
+          <t>-5,41; 1,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 4,64</t>
+          <t>-0,16; 6,63</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-3,86%</t>
+          <t>-6,11%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-3,68%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-2,71%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 23,0</t>
+          <t>-17,24; 26,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,8; -1,19</t>
+          <t>-35,6; -3,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 16,09</t>
+          <t>-22,15; 13,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 29,22</t>
+          <t>-3,13; 30,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 22,27</t>
+          <t>-11,17; 21,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,21; 25,9</t>
+          <t>6,22; 37,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 21,2</t>
+          <t>-4,96; 20,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 6,43</t>
+          <t>-16,63; 6,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-35,96; 15,48</t>
+          <t>-0,43; 23,27</t>
         </is>
       </c>
     </row>
